--- a/business/email-assets/trial-pack/2-90-Day-Cash-Flow.xlsx
+++ b/business/email-assets/trial-pack/2-90-Day-Cash-Flow.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Lowest balance</t>
   </si>
   <si>
-    <t xml:space="preserve">TradeSheets free trial pack · Blue text = your inputs · Black = formulas (don't overwrite) · Full custom setup: reply to the email you got this from.</t>
+    <t xml:space="preserve">TradeSheets free trial pack · Blue text = your inputs · Black = locked formulas (Review &gt; Unprotect Sheet to change) · Full custom setup: reply to the email you got this from.</t>
   </si>
 </sst>
 </file>
@@ -252,17 +252,17 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
@@ -276,9 +276,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -1220,6 +1220,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <mergeCells count="5">
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C5"/>
